--- a/assessment_forms/035_home_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/035_home_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single_family_home',_'value':_'single_family_home'}</t>
+          <t>single_family_home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Single Family Home', 'value': 'Single Family Home'}</t>
+          <t>Single Family Home</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'condo',_'value':_'condo'}</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Condo', 'value': 'Condo'}</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'townhouse',_'value':_'townhouse'}</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Townhouse', 'value': 'Townhouse'}</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Completed', 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Completed', 'value': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'scheduled',_'value':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Scheduled', 'value': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
